--- a/Report/ReportAdd.xlsx
+++ b/Report/ReportAdd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4AC357-51AB-4618-BFEB-134B8DA54592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A235B24-759D-41E0-8898-47A97DEE45AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,10 +603,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" style="5" customWidth="1"/>
     <col min="7" max="7" width="29.6640625" customWidth="1"/>
     <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26.44140625" customWidth="1"/>
